--- a/artfynd/A 38855-2022 artfynd.xlsx
+++ b/artfynd/A 38855-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38855-2022 artfynd.xlsx
+++ b/artfynd/A 38855-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104322159</v>
+        <v>104319688</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,12 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -725,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hofors, Gstr</t>
+          <t>Hofors Kårsbergsvägen, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583208.0923753195</v>
+        <v>583174</v>
       </c>
       <c r="R2" t="n">
-        <v>6697647.694402357</v>
+        <v>6697675</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,27 +779,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maj-Lis Koivisto</t>
+          <t>marianne johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maj-Lis Koivisto</t>
+          <t>marianne johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104320841</v>
+        <v>104320743</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,29 +821,26 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hofors Kårsbergsv, Gstr</t>
+          <t>Hofors Kårsbergsv , Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583067.2074746781</v>
+        <v>583071</v>
       </c>
       <c r="R3" t="n">
-        <v>6697725.029930603</v>
+        <v>6697721</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -890,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,6 +891,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -927,15 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104319688</v>
+        <v>104320841</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,7 +940,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -972,14 +955,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hofors Kårsbergsvägen, Gstr</t>
+          <t>Hofors Kårsbergsv, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583173.8112325585</v>
+        <v>583068</v>
       </c>
       <c r="R4" t="n">
-        <v>6697674.586886453</v>
+        <v>6697725</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1021,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,64 +1031,56 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104319863</v>
+        <v>104320971</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hofors Kårsbergsv, Gstr</t>
+          <t>Hofors Kårsbergsv , Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583150.0831499592</v>
+        <v>583161</v>
       </c>
       <c r="R5" t="n">
-        <v>6697673.054622693</v>
+        <v>6697806</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1137,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1147,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,6 +1131,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1177,12 +1153,7 @@
         <v>104321319</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583149.1938310231</v>
+        <v>583149</v>
       </c>
       <c r="R6" t="n">
-        <v>6697755.079527058</v>
+        <v>6697755</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1298,15 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104320743</v>
+        <v>104321954</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583071.2563370219</v>
+        <v>583176</v>
       </c>
       <c r="R7" t="n">
-        <v>6697721.168637986</v>
+        <v>6697716</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1384,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1360,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,15 +1388,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104321954</v>
+        <v>104322159</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,26 +1418,29 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hofors Kårsbergsv , Gstr</t>
+          <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583175.356833201</v>
+        <v>583209</v>
       </c>
       <c r="R8" t="n">
-        <v>6697715.150931483</v>
+        <v>6697648</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1508,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1518,7 +1482,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,22 +1491,142 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Maj-Lis Koivisto</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maj-Lis Koivisto</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104319863</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hofors Kårsbergsv, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>583150</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6697674</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>marianne johansson</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>marianne johansson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38855-2022 artfynd.xlsx
+++ b/artfynd/A 38855-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104319688</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320743</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320841</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1147,6 +1167,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320971</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1266,6 +1291,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104321319</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1385,6 +1415,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104321954</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1506,6 +1541,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104322159</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1627,8 +1667,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104319863</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>